--- a/Tabela3_validacao.xlsx
+++ b/Tabela3_validacao.xlsx
@@ -535,7 +535,7 @@
         <v>-1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-1.001778</v>
+        <v>-1.272942</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>-1</v>
@@ -555,10 +555,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.322911</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>-1</v>
+        <v>0.220789</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -575,7 +575,7 @@
         <v>-1</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.913358</v>
+        <v>-0.810731</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>-1</v>
@@ -595,10 +595,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.21971</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-1</v>
+        <v>0.075464</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -615,7 +615,7 @@
         <v>-1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-1.001851</v>
+        <v>-1.277956</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>-1</v>
@@ -635,7 +635,7 @@
         <v>-1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0.987074</v>
+        <v>-1.135135</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>-1</v>
@@ -655,7 +655,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.965959</v>
+        <v>1.281006</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>1</v>
@@ -675,7 +675,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.322671</v>
+        <v>1.409181</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>1</v>
@@ -695,10 +695,10 @@
         <v>-1</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.467749</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>-1</v>
+        <v>0.001265</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -715,7 +715,7 @@
         <v>-1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.995932</v>
+        <v>-1.172696</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>-1</v>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
